--- a/spec/CAMPAIGN-TEMPLATE.xlsx
+++ b/spec/CAMPAIGN-TEMPLATE.xlsx
@@ -11,7 +11,9 @@
     <sheet name="Campaign" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Ad Sets" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Ads" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Reference" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Languages" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Countries" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Reference" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42,13 +44,13 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001F3864"/>
-      <sz val="15"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -62,7 +64,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +96,11 @@
         <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -121,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -150,7 +157,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -159,12 +165,18 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,12 +542,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C31"/>
+  <dimension ref="B1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="96" customWidth="1" min="3" max="3"/>
+    <col width="104" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,7 +557,7 @@
     <row r="2">
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Meta Campaign Spec — fill this in, hand it to Claude</t>
+          <t>Meta Campaign Spec</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -562,7 +574,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Fill the three tabs below, save the file, then tell Claude:</t>
+          <t>Fill the tabs below, save, then tell Claude: "Build the campaign in &lt;file&gt;.xlsx"</t>
         </is>
       </c>
     </row>
@@ -570,7 +582,7 @@
       <c r="B5" s="1" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   "Build the campaign in &lt;filename&gt;.xlsx"</t>
+          <t>Claude checks every row, tells you what's missing, previews, and waits for your OK.</t>
         </is>
       </c>
     </row>
@@ -578,63 +590,67 @@
       <c r="B6" s="1" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Claude reads it, tells you what is missing, shows a preview, and waits for your OK.</t>
+          <t>Everything is created PAUSED. Nothing spends until you launch it in Ads Manager.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Nothing is created until you say go. Everything is created PAUSED.</t>
-        </is>
-      </c>
+      <c r="C7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="B8" s="1" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Colour legend</t>
+        </is>
+      </c>
       <c r="C8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Colour legend</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Yellow cell</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>REQUIRED. Claude refuses to build without it. Nothing is ever guessed.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Yellow cells</t>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Light orange</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>REQUIRED. Claude will refuse to build if these are empty. Nothing is guessed.</t>
+          <t>Optional. Blank means: use the Campaign tab default, or let Meta decide.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Light orange</t>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Grey row</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Optional. Leave blank to use the default from the Campaign tab.</t>
+          <t>Example row. Delete before handing over.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Grey row</t>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Dark blue header</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Example row. Delete it before you hand the file over.</t>
+          <t>Required column.        Mid blue header: optional column.</t>
         </is>
       </c>
     </row>
@@ -645,7 +661,7 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>The three tabs</t>
+          <t>Tabs</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
@@ -658,7 +674,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>One campaign. Its objective, budget mode, and the defaults every ad inherits.</t>
+          <t>The campaign, plus defaults every ad set and ad inherits.</t>
         </is>
       </c>
     </row>
@@ -670,7 +686,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>One row per ad set. Targeting, optimisation, and budget if you use ABO.</t>
+          <t>One row per ad set. Budget, targeting, placements, schedule.</t>
         </is>
       </c>
     </row>
@@ -682,127 +698,163 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>One row per ad. This is the bulk sheet — hundreds or thousands of rows is fine.</t>
+          <t>One row per ad. The bulk sheet. Thousands of rows is fine.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Reference</t>
+          <t xml:space="preserve">  4. Languages</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Valid values for every dropdown. Read-only.</t>
+          <t>The 92 languages Meta accepts, with their IDs. Copy names into Ad Sets.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="2" t="inlineStr"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Countries</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>ISO country codes. Copy codes into Ad Sets.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Two rules that trip people up</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Reference</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Every valid value for every dropdown field.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Budgets are in MINOR units</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Cents. 20000 = 200.00 in your account currency. 100 = 1.00. Never write 200.00.</t>
-        </is>
-      </c>
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Rules that trip people up</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Money is in MINOR units</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Cents. 20000 = 200.00. 100 = 1.00. Never write 200.00 or £200.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  CBO or ABO, never both</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>CBO: budget on the Campaign tab, leave ad set budgets blank.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>ABO: leave the campaign budget blank, fill a budget on EVERY ad set row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>CBO: budget on Campaign tab, ad set budgets blank.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Creative files</t>
-        </is>
-      </c>
+      <c r="B25" s="1" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Put images/videos in the creatives/ folder. The Ads tab references them by filename.</t>
+          <t>ABO: Campaign budget blank, a budget on EVERY ad set row.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="1" t="inlineStr"/>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Lists go in one cell</t>
+        </is>
+      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Reuse the same filename across rows freely — each file is uploaded to Meta only once.</t>
+          <t>Comma-separated: countries "GB,IE"  languages "English (UK),Polish"</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="2" t="inlineStr"/>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Blank = Meta default</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>An empty optional cell means Meta decides (e.g. all placements, all genders).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>EU targeting</t>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EU targeting</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>If any ad set targets an EU country, dsa_beneficiary is REQUIRED — the legal name</t>
+          <t>dsa_beneficiary is REQUIRED if any country is in the EU. Legal advertiser name.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>of the advertiser. Meta rejects the ad set without it. It is a legal disclosure; get it right.</t>
-        </is>
-      </c>
+      <c r="C29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="B30" s="1" t="inlineStr"/>
-      <c r="C30" s="2" t="inlineStr"/>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Creatives</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Put images/videos in the creatives/ folder. Reference them by filename only.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>What Claude will NOT do</t>
-        </is>
-      </c>
+      <c r="B31" s="1" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Invent a budget, Page, pixel, audience or URL. Un-pause anything. Launch anything.</t>
+          <t>Reuse a filename across rows freely. Each file uploads to Meta once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="1" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Never guessed</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Budget, Page, pixel, audience, destination URL. Missing one stops the run.</t>
         </is>
       </c>
     </row>
@@ -817,12 +869,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="76" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="86" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,7 +907,7 @@
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>The ad account. Always starts with act_</t>
+          <t>Ad account. Always starts with act_</t>
         </is>
       </c>
     </row>
@@ -867,12 +919,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Q3 Prospecting — UK</t>
+          <t>Q3 Prospecting UK</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Must be unique in the account. Claude aborts if it already exists.</t>
+          <t>Unique in the account. Claude aborts if it already exists.</t>
         </is>
       </c>
     </row>
@@ -889,231 +941,349 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Dropdown. Drives which optimisation goals are valid.</t>
+          <t>Dropdown. Decides which optimisation goals are valid.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>budget_mode</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>CBO</t>
+          <t>buying_type</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>AUCTION</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>CBO = one budget on the campaign. ABO = a budget on each ad set.</t>
+          <t>AUCTION (normal) or RESERVED. Blank = AUCTION.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>daily_budget_minor</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>20000</v>
+          <t>budget_mode</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>CBO</t>
+        </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>CBO only. MINOR units — 20000 = 200.00. Leave blank for ABO.</t>
+          <t>CBO = one budget on the campaign. ABO = a budget per ad set.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>special_ad_categories</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr"/>
+          <t>daily_budget_minor</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>20000</v>
+      </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>HOUSING / EMPLOYMENT / CREDIT / ISSUES_ELECTIONS_POLITICS. Blank for none.</t>
+          <t>CBO only. MINOR units: 20000 = 200.00. Blank for ABO.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr"/>
-      <c r="B8" s="15" t="inlineStr"/>
-      <c r="C8" s="11" t="inlineStr"/>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>lifetime_budget_minor</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>CBO alternative to daily. Set one or the other, not both.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>DEFAULTS</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>every ad inherits these unless its own row overrides</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr"/>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>bid_strategy</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>LOWEST_COST_WITHOUT_CAP</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Blank = lowest cost, no cap.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>page_id</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>100000000000001</t>
-        </is>
-      </c>
+          <t>spend_cap_minor</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr"/>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Facebook Page the ads run from. Get it from: discover.py act_&lt;id&gt;</t>
+          <t>Lifetime ceiling for the whole campaign. Blank = none.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>instagram_user_id</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr"/>
+          <t>start_time</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr"/>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Leave blank if the account has no linked Instagram account.</t>
+          <t>Optional. Format 2026-09-01T00:00:00+0300</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>pixel_id</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>200000000000002</t>
-        </is>
-      </c>
+          <t>end_time</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr"/>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Required for conversion objectives.</t>
+          <t>Optional. Required if you set a lifetime budget.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>custom_event_type</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>PURCHASE</t>
-        </is>
-      </c>
+          <t>special_ad_categories</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr"/>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>The conversion event, e.g. PURCHASE. Conversion objectives only.</t>
+          <t>HOUSING / EMPLOYMENT / CREDIT / ISSUES_ELECTIONS_POLITICS. Blank = none.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>https://example.com/lp</t>
-        </is>
-      </c>
+          <t>special_ad_category_country</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr"/>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Default destination URL. Never guessed.</t>
+          <t>ISO code, e.g. US. Only if a special category is set.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>cta</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>SHOP_NOW</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Default call-to-action button.</t>
-        </is>
-      </c>
+      <c r="A15" s="13" t="inlineStr"/>
+      <c r="B15" s="14" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>url_tags</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>utm_source=facebook&amp;utm_medium=paid&amp;utm_campaign=q3</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>UTM string appended to every link.</t>
-        </is>
-      </c>
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>DEFAULTS</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>inherited by every ad set and ad unless its row overrides</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>dsa_beneficiary</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>Example Ltd</t>
+          <t>page_id</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>100000000000001</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>REQUIRED if targeting the EU. Legal name of the advertiser.</t>
+          <t>Facebook Page the ads run from. Find it: discover.py act_&lt;id&gt;</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
+          <t>instagram_user_id</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr"/>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Blank if the account has no linked Instagram account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>pixel_id</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>200000000000002</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Required for conversion objectives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>custom_event_type</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>PURCHASE</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Conversion event. Conversion objectives only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>https://example.com/lp</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Default destination URL. Never guessed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>display_link</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr"/>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Optional vanity URL shown on the ad, e.g. example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>cta</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>SHOP_NOW</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Default call-to-action button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>url_tags</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>utm_source=facebook&amp;utm_medium=paid&amp;utm_campaign=q3</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>UTMs appended to every link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>dsa_beneficiary</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Example Ltd</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>REQUIRED if targeting the EU. Legal name of the advertiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
           <t>dsa_payor</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr"/>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Defaults to dsa_beneficiary if left blank.</t>
+      <c r="B26" s="12" t="inlineStr"/>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Blank = same as dsa_beneficiary.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="6">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OUTCOME_SALES,OUTCOME_LEADS,OUTCOME_TRAFFIC,OUTCOME_AWARENESS,OUTCOME_ENGAGEMENT,OUTCOME_APP_PROMOTION"</formula1>
     </dataValidation>
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"AUCTION,RESERVED"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CBO,ABO"</formula1>
     </dataValidation>
-    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"LOWEST_COST_WITHOUT_CAP,LOWEST_COST_WITH_BID_CAP,COST_CAP"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PURCHASE,ADD_TO_CART,INITIATE_CHECKOUT,COMPLETE_REGISTRATION,LEAD,VIEW_CONTENT,SEARCH,ADD_PAYMENT_INFO,SUBSCRIBE,START_TRIAL"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"LEARN_MORE,SHOP_NOW,SIGN_UP,SUBSCRIBE,BOOK_TRAVEL,CONTACT_US,DOWNLOAD,GET_OFFER,GET_QUOTE,APPLY_NOW,BUY_NOW,ORDER_NOW,GET_STARTED,SEND_MESSAGE,WATCH_MORE,NO_BUTTON"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"PURCHASE,ADD_TO_CART,INITIATE_CHECKOUT,COMPLETE_REGISTRATION,LEAD,VIEW_CONTENT,SEARCH,ADD_PAYMENT_INFO,SUBSCRIBE,START_TRIAL"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1126,24 +1296,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>adset_name</t>
         </is>
@@ -1155,45 +1343,135 @@
       </c>
       <c r="C1" s="18" t="inlineStr">
         <is>
+          <t>lifetime_budget_minor</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
           <t>optimization_goal</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>billing_event</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>bid_strategy</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t>bid_amount_minor</t>
+        </is>
+      </c>
+      <c r="H1" s="17" t="inlineStr">
         <is>
           <t>countries</t>
         </is>
       </c>
-      <c r="F1" s="18" t="inlineStr">
+      <c r="I1" s="18" t="inlineStr">
+        <is>
+          <t>excluded_countries</t>
+        </is>
+      </c>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
+          <t>cities</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
+          <t>regions</t>
+        </is>
+      </c>
+      <c r="L1" s="18" t="inlineStr">
+        <is>
+          <t>location_types</t>
+        </is>
+      </c>
+      <c r="M1" s="18" t="inlineStr">
+        <is>
+          <t>languages</t>
+        </is>
+      </c>
+      <c r="N1" s="18" t="inlineStr">
+        <is>
+          <t>genders</t>
+        </is>
+      </c>
+      <c r="O1" s="18" t="inlineStr">
         <is>
           <t>age_min</t>
         </is>
       </c>
-      <c r="G1" s="18" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>age_max</t>
         </is>
       </c>
-      <c r="H1" s="18" t="inlineStr">
+      <c r="Q1" s="18" t="inlineStr">
+        <is>
+          <t>interests</t>
+        </is>
+      </c>
+      <c r="R1" s="18" t="inlineStr">
+        <is>
+          <t>excluded_interests</t>
+        </is>
+      </c>
+      <c r="S1" s="18" t="inlineStr">
+        <is>
+          <t>custom_audiences</t>
+        </is>
+      </c>
+      <c r="T1" s="18" t="inlineStr">
+        <is>
+          <t>excluded_custom_audiences</t>
+        </is>
+      </c>
+      <c r="U1" s="18" t="inlineStr">
+        <is>
+          <t>advantage_audience</t>
+        </is>
+      </c>
+      <c r="V1" s="18" t="inlineStr">
+        <is>
+          <t>device_platforms</t>
+        </is>
+      </c>
+      <c r="W1" s="18" t="inlineStr">
+        <is>
+          <t>publisher_platforms</t>
+        </is>
+      </c>
+      <c r="X1" s="18" t="inlineStr">
+        <is>
+          <t>facebook_positions</t>
+        </is>
+      </c>
+      <c r="Y1" s="18" t="inlineStr">
+        <is>
+          <t>instagram_positions</t>
+        </is>
+      </c>
+      <c r="Z1" s="18" t="inlineStr">
         <is>
           <t>custom_event_type</t>
         </is>
       </c>
-      <c r="I1" s="18" t="inlineStr">
+      <c r="AA1" s="18" t="inlineStr">
         <is>
           <t>start_time</t>
         </is>
       </c>
-      <c r="J1" s="18" t="inlineStr">
+      <c r="AB1" s="18" t="inlineStr">
         <is>
           <t>end_time</t>
         </is>
       </c>
-      <c r="K1" s="18" t="inlineStr">
+      <c r="AC1" s="18" t="inlineStr">
         <is>
           <t>dsa_beneficiary</t>
         </is>
@@ -1202,39 +1480,81 @@
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Q3 — UK — Broad 18-45</t>
+          <t>Q3 UK Broad 18-45</t>
         </is>
       </c>
       <c r="B2" s="19" t="inlineStr"/>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr"/>
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>OFFSITE_CONVERSIONS</t>
         </is>
       </c>
-      <c r="D2" s="19" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>IMPRESSIONS</t>
         </is>
       </c>
-      <c r="E2" s="19" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr"/>
+      <c r="G2" s="19" t="inlineStr"/>
+      <c r="H2" s="19" t="inlineStr">
         <is>
           <t>GB</t>
-        </is>
-      </c>
-      <c r="F2" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="G2" s="19" t="n">
-        <v>45</v>
-      </c>
-      <c r="H2" s="19" t="inlineStr">
-        <is>
-          <t>PURCHASE</t>
         </is>
       </c>
       <c r="I2" s="19" t="inlineStr"/>
       <c r="J2" s="19" t="inlineStr"/>
-      <c r="K2" s="19" t="inlineStr">
+      <c r="K2" s="19" t="inlineStr"/>
+      <c r="L2" s="19" t="inlineStr">
+        <is>
+          <t>home+recent</t>
+        </is>
+      </c>
+      <c r="M2" s="19" t="inlineStr">
+        <is>
+          <t>English (UK)</t>
+        </is>
+      </c>
+      <c r="N2" s="19" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O2" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="P2" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q2" s="19" t="inlineStr"/>
+      <c r="R2" s="19" t="inlineStr"/>
+      <c r="S2" s="19" t="inlineStr"/>
+      <c r="T2" s="19" t="inlineStr"/>
+      <c r="U2" s="19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V2" s="19" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="W2" s="19" t="inlineStr">
+        <is>
+          <t>facebook,instagram</t>
+        </is>
+      </c>
+      <c r="X2" s="19" t="inlineStr"/>
+      <c r="Y2" s="19" t="inlineStr"/>
+      <c r="Z2" s="19" t="inlineStr">
+        <is>
+          <t>PURCHASE</t>
+        </is>
+      </c>
+      <c r="AA2" s="19" t="inlineStr"/>
+      <c r="AB2" s="19" t="inlineStr"/>
+      <c r="AC2" s="19" t="inlineStr">
         <is>
           <t>Example Ltd</t>
         </is>
@@ -1243,39 +1563,101 @@
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>Q3 — UK — Retarget 30d</t>
+          <t>Q3 UK Retarget 30d</t>
         </is>
       </c>
       <c r="B3" s="19" t="inlineStr"/>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr"/>
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>OFFSITE_CONVERSIONS</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>IMPRESSIONS</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F3" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="G3" s="19" t="n">
-        <v>65</v>
-      </c>
+      <c r="F3" s="19" t="inlineStr"/>
+      <c r="G3" s="19" t="inlineStr"/>
       <c r="H3" s="19" t="inlineStr">
         <is>
+          <t>GB,IE</t>
+        </is>
+      </c>
+      <c r="I3" s="19" t="inlineStr"/>
+      <c r="J3" s="19" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="K3" s="19" t="inlineStr"/>
+      <c r="L3" s="19" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="M3" s="19" t="inlineStr">
+        <is>
+          <t>English (UK),English (US)</t>
+        </is>
+      </c>
+      <c r="N3" s="19" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="O3" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="P3" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q3" s="19" t="inlineStr"/>
+      <c r="R3" s="19" t="inlineStr"/>
+      <c r="S3" s="19" t="inlineStr">
+        <is>
+          <t>Website visitors 30d</t>
+        </is>
+      </c>
+      <c r="T3" s="19" t="inlineStr">
+        <is>
+          <t>Purchasers 180d</t>
+        </is>
+      </c>
+      <c r="U3" s="19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="V3" s="19" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="W3" s="19" t="inlineStr">
+        <is>
+          <t>facebook,instagram</t>
+        </is>
+      </c>
+      <c r="X3" s="19" t="inlineStr">
+        <is>
+          <t>feed,facebook_reels</t>
+        </is>
+      </c>
+      <c r="Y3" s="19" t="inlineStr">
+        <is>
+          <t>stream,reels</t>
+        </is>
+      </c>
+      <c r="Z3" s="19" t="inlineStr">
+        <is>
           <t>PURCHASE</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr"/>
-      <c r="J3" s="19" t="inlineStr"/>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="AA3" s="19" t="inlineStr"/>
+      <c r="AB3" s="19" t="inlineStr"/>
+      <c r="AC3" s="19" t="inlineStr">
         <is>
           <t>Example Ltd</t>
         </is>
@@ -1284,33 +1666,97 @@
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
         <is>
-          <t>↑ delete the grey example rows before handing this over</t>
+          <t>^ delete the grey example rows before handing this over</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>countries: comma-separated ISO codes, e.g. GB,IE  ·  daily_budget_minor: ABO only, blank for CBO</t>
+          <t>countries / excluded_countries: ISO codes, comma separated. See the Countries tab. e.g. GB,IE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>start_time / end_time: optional, format 2026-09-01T00:00:00+0300</t>
+          <t>cities / regions: names, comma separated. e.g. London,Manchester  (Claude resolves them to Meta IDs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>location_types: home+recent (default), home, recent, travel_in</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>languages: names EXACTLY as on the Languages tab, comma separated. Blank = all languages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>genders: All / Men / Women.   advantage_audience: yes lets Meta expand beyond your targeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>interests / custom_audiences: names, comma separated. Claude resolves and CONFIRMS each one before building.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>publisher_platforms / positions: blank = Advantage+ placements (all). Fill only to restrict.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>budgets: fill daily OR lifetime, never both. Leave BOTH blank if the campaign is CBO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>start_time / end_time: 2026-09-01T00:00:00+0300</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="C2:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"OFFSITE_CONVERSIONS,LANDING_PAGE_VIEWS,LINK_CLICKS,IMPRESSIONS,REACH,LEAD_GENERATION,THRUPLAY"</formula1>
+  <dataValidations count="8">
+    <dataValidation sqref="D2:D3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"OFFSITE_CONVERSIONS,LANDING_PAGE_VIEWS,LINK_CLICKS,IMPRESSIONS,REACH,LEAD_GENERATION,THRUPLAY,VALUE"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"IMPRESSIONS,LINK_CLICKS,POST_ENGAGEMENT"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"LOWEST_COST_WITHOUT_CAP,LOWEST_COST_WITH_BID_CAP,COST_CAP"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"home+recent,home,recent,travel_in"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"All,Men,Women"</formula1>
+    </dataValidation>
+    <dataValidation sqref="U2:U3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+    <dataValidation sqref="V2:V3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"All,mobile,desktop"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Z2:Z3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PURCHASE,ADD_TO_CART,INITIATE_CHECKOUT,COMPLETE_REGISTRATION,LEAD,VIEW_CONTENT,SEARCH,ADD_PAYMENT_INFO,SUBSCRIBE,START_TRIAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1324,43 +1770,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="64" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>adset_name</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>ad_name</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>creative_file</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t>body</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
         <is>
           <t>headline</t>
         </is>
@@ -1382,24 +1830,34 @@
       </c>
       <c r="I1" s="18" t="inlineStr">
         <is>
+          <t>display_link</t>
+        </is>
+      </c>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
           <t>url_tags</t>
         </is>
       </c>
-      <c r="J1" s="18" t="inlineStr">
+      <c r="K1" s="18" t="inlineStr">
         <is>
           <t>page_id</t>
+        </is>
+      </c>
+      <c r="L1" s="18" t="inlineStr">
+        <is>
+          <t>instagram_user_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Q3 — UK — Broad 18-45</t>
+          <t>Q3 UK Broad 18-45</t>
         </is>
       </c>
       <c r="B2" s="21" t="inlineStr">
         <is>
-          <t>Q3-UK-01-price-hook</t>
+          <t>Q3-UK-01-price</t>
         </is>
       </c>
       <c r="C2" s="21" t="inlineStr">
@@ -1409,7 +1867,7 @@
       </c>
       <c r="D2" s="21" t="inlineStr">
         <is>
-          <t>Three months of clear skin, or your money back. Over 12,000 five-star reviews.</t>
+          <t>Three months of clear skin, or your money back. Over 12,000 five star reviews.</t>
         </is>
       </c>
       <c r="E2" s="21" t="inlineStr">
@@ -1432,18 +1890,24 @@
           <t>https://example.com/lp?v=a</t>
         </is>
       </c>
-      <c r="I2" s="21" t="inlineStr"/>
+      <c r="I2" s="21" t="inlineStr">
+        <is>
+          <t>example.com</t>
+        </is>
+      </c>
       <c r="J2" s="21" t="inlineStr"/>
+      <c r="K2" s="21" t="inlineStr"/>
+      <c r="L2" s="21" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>Q3 — UK — Broad 18-45</t>
+          <t>Q3 UK Broad 18-45</t>
         </is>
       </c>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t>Q3-UK-02-ugc-video</t>
+          <t>Q3-UK-02-ugc</t>
         </is>
       </c>
       <c r="C3" s="21" t="inlineStr">
@@ -1453,7 +1917,7 @@
       </c>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t>I tried everything before this. Six weeks in — see for yourself.</t>
+          <t>I tried everything before this. Six weeks in, see for yourself.</t>
         </is>
       </c>
       <c r="E3" s="21" t="inlineStr">
@@ -1474,11 +1938,13 @@
       </c>
       <c r="I3" s="21" t="inlineStr"/>
       <c r="J3" s="21" t="inlineStr"/>
+      <c r="K3" s="21" t="inlineStr"/>
+      <c r="L3" s="21" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>Q3 — UK — Retarget 30d</t>
+          <t>Q3 UK Retarget 30d</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
@@ -1498,7 +1964,7 @@
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>20% off — today only</t>
+          <t>20% off today only</t>
         </is>
       </c>
       <c r="F4" s="21" t="inlineStr">
@@ -1518,38 +1984,40 @@
       </c>
       <c r="I4" s="21" t="inlineStr"/>
       <c r="J4" s="21" t="inlineStr"/>
+      <c r="K4" s="21" t="inlineStr"/>
+      <c r="L4" s="21" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>↑ delete the grey example rows. One row per ad — thousands is fine.</t>
+          <t>^ delete the grey example rows. One row per ad. Thousands is fine.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>adset_name MUST match a row on the Ad Sets tab exactly (copy/paste it).</t>
+          <t>adset_name MUST match a row on the Ad Sets tab exactly. Copy and paste it.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>creative_file: filename inside creatives/  ·  .jpg .png = image, .mp4 .mov = video</t>
+          <t>creative_file: filename inside creatives/   .jpg .png = image,  .mp4 .mov = video</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>cta / link / url_tags / page_id: leave blank to inherit from the Campaign tab.</t>
+          <t>cta / link / url_tags / page_id / instagram_user_id: blank inherits the Campaign tab default.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G3000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"LEARN_MORE,SHOP_NOW,SIGN_UP,SUBSCRIBE,BOOK_TRAVEL,CONTACT_US,DOWNLOAD,GET_OFFER,GET_QUOTE,APPLY_NOW,BUY_NOW,ORDER_NOW,GET_STARTED,SEND_MESSAGE,WATCH_MORE,NO_BUTTON"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1563,171 +2031,1935 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:B95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Objectives</t>
+          <t>Language name (copy this)</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>Optimization goals</t>
-        </is>
-      </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>Billing events</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>Conversion events</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>Call to action</t>
+          <t>Meta locale ID</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>OUTCOME_SALES</t>
-        </is>
-      </c>
-      <c r="B2" s="22" t="inlineStr">
-        <is>
-          <t>OFFSITE_CONVERSIONS</t>
-        </is>
-      </c>
-      <c r="C2" s="22" t="inlineStr">
-        <is>
-          <t>IMPRESSIONS</t>
-        </is>
-      </c>
-      <c r="D2" s="22" t="inlineStr">
-        <is>
-          <t>PURCHASE</t>
-        </is>
-      </c>
-      <c r="E2" s="22" t="inlineStr">
-        <is>
-          <t>LEARN_MORE</t>
-        </is>
+          <t>Afrikaans</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="22" t="inlineStr">
         <is>
-          <t>OUTCOME_LEADS</t>
-        </is>
-      </c>
-      <c r="B3" s="22" t="inlineStr">
-        <is>
-          <t>LANDING_PAGE_VIEWS</t>
-        </is>
-      </c>
-      <c r="C3" s="22" t="inlineStr">
-        <is>
-          <t>LINK_CLICKS</t>
-        </is>
-      </c>
-      <c r="D3" s="22" t="inlineStr">
-        <is>
-          <t>ADD_TO_CART</t>
-        </is>
-      </c>
-      <c r="E3" s="22" t="inlineStr">
-        <is>
-          <t>SHOP_NOW</t>
-        </is>
+          <t>Albanian</t>
+        </is>
+      </c>
+      <c r="B3" s="22" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
         <is>
-          <t>OUTCOME_TRAFFIC</t>
-        </is>
-      </c>
-      <c r="B4" s="22" t="inlineStr">
-        <is>
-          <t>LINK_CLICKS</t>
-        </is>
-      </c>
-      <c r="C4" s="22" t="inlineStr">
-        <is>
-          <t>POST_ENGAGEMENT</t>
-        </is>
-      </c>
-      <c r="D4" s="22" t="inlineStr">
-        <is>
-          <t>INITIATE_CHECKOUT</t>
-        </is>
-      </c>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>SIGN_UP</t>
-        </is>
+          <t>Arabic</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>OUTCOME_AWARENESS</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>IMPRESSIONS</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>COMPLETE_REGISTRATION</t>
-        </is>
-      </c>
-      <c r="E5" s="22" t="inlineStr">
-        <is>
-          <t>SUBSCRIBE</t>
-        </is>
+          <t>Armenian</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t>OUTCOME_ENGAGEMENT</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>REACH</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>LEAD</t>
-        </is>
-      </c>
-      <c r="E6" s="22" t="inlineStr">
-        <is>
-          <t>BOOK_TRAVEL</t>
-        </is>
+          <t>Azerbaijani</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
         <is>
+          <t>Basque</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Belarusian</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>Bengali</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Bosnian</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Bulgarian</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Catalan</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Cebuano</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Chinese (All)</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Croatian</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Czech</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Danish</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Dutch</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>English (All)</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="n">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>English (UK)</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>English (US)</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Esperanto</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Estonian</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Faroese</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Filipino</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>Finnish</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Flemish</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>French (All)</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>French (Canada)</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>French (France)</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>Frisian</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Galician</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>Georgian</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>Greek</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Gujarati</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>Hebrew</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>Hungarian</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>Icelandic</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>Indonesian</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>Irish</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>Italian</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>Japanese (Kansai)</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>Javanese</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>Kazakh</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>Khmer</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>Korean</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>Latvian</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>Lithuanian</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>Macedonian</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>Malay</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>Marathi</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>Mongolian</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>Nepali</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>Northern Kurdish (Kurmanji)</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>Norwegian (bokmal)</t>
+        </is>
+      </c>
+      <c r="B61" s="22" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>Norwegian (nynorsk)</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>Pashto</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>Persian</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>Polish</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>Portuguese (All)</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="n">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>Portuguese (Brazil)</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>Portuguese (Portugal)</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="22" t="inlineStr">
+        <is>
+          <t>Punjabi</t>
+        </is>
+      </c>
+      <c r="B69" s="22" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="22" t="inlineStr">
+        <is>
+          <t>Romanian</t>
+        </is>
+      </c>
+      <c r="B70" s="22" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="inlineStr">
+        <is>
+          <t>Russian</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="22" t="inlineStr">
+        <is>
+          <t>Serbian</t>
+        </is>
+      </c>
+      <c r="B72" s="22" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="22" t="inlineStr">
+        <is>
+          <t>Simplified Chinese (China)</t>
+        </is>
+      </c>
+      <c r="B73" s="22" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="22" t="inlineStr">
+        <is>
+          <t>Sinhala</t>
+        </is>
+      </c>
+      <c r="B74" s="22" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="22" t="inlineStr">
+        <is>
+          <t>Slovak</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="22" t="inlineStr">
+        <is>
+          <t>Slovenian</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="22" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="B77" s="22" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="22" t="inlineStr">
+        <is>
+          <t>Spanish (All)</t>
+        </is>
+      </c>
+      <c r="B78" s="22" t="n">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="22" t="inlineStr">
+        <is>
+          <t>Spanish (Spain)</t>
+        </is>
+      </c>
+      <c r="B79" s="22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="22" t="inlineStr">
+        <is>
+          <t>Swahili</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="22" t="inlineStr">
+        <is>
+          <t>Swedish</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="22" t="inlineStr">
+        <is>
+          <t>Tajik</t>
+        </is>
+      </c>
+      <c r="B82" s="22" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="22" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="B83" s="22" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="22" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="B84" s="22" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="22" t="inlineStr">
+        <is>
+          <t>Thai</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="22" t="inlineStr">
+        <is>
+          <t>Traditional Chinese (Hong Kong)</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="22" t="inlineStr">
+        <is>
+          <t>Traditional Chinese (Taiwan)</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="22" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="22" t="inlineStr">
+        <is>
+          <t>Ukrainian</t>
+        </is>
+      </c>
+      <c r="B89" s="22" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>Urdu</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="22" t="inlineStr">
+        <is>
+          <t>Uzbek</t>
+        </is>
+      </c>
+      <c r="B91" s="22" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="22" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="B92" s="22" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="22" t="inlineStr">
+        <is>
+          <t>Welsh</t>
+        </is>
+      </c>
+      <c r="B93" s="22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="20" t="inlineStr">
+        <is>
+          <t>92 languages, pulled live from Meta. Copy names into the Ad Sets 'languages' column.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ISO code (copy this)</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="B3" s="22" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>Common markets. Any ISO 3166-1 alpha-2 code works, not just these.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Objectives</t>
+        </is>
+      </c>
+      <c r="B1" s="23" t="inlineStr">
+        <is>
+          <t>Optimization goals</t>
+        </is>
+      </c>
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>Billing events</t>
+        </is>
+      </c>
+      <c r="D1" s="23" t="inlineStr">
+        <is>
+          <t>Bid strategies</t>
+        </is>
+      </c>
+      <c r="E1" s="23" t="inlineStr">
+        <is>
+          <t>Conversion events</t>
+        </is>
+      </c>
+      <c r="F1" s="23" t="inlineStr">
+        <is>
+          <t>Call to action</t>
+        </is>
+      </c>
+      <c r="G1" s="23" t="inlineStr">
+        <is>
+          <t>Genders</t>
+        </is>
+      </c>
+      <c r="H1" s="23" t="inlineStr">
+        <is>
+          <t>Location types</t>
+        </is>
+      </c>
+      <c r="I1" s="23" t="inlineStr">
+        <is>
+          <t>Device platforms</t>
+        </is>
+      </c>
+      <c r="J1" s="23" t="inlineStr">
+        <is>
+          <t>Publisher platforms</t>
+        </is>
+      </c>
+      <c r="K1" s="23" t="inlineStr">
+        <is>
+          <t>Facebook positions</t>
+        </is>
+      </c>
+      <c r="L1" s="23" t="inlineStr">
+        <is>
+          <t>Instagram positions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>OUTCOME_SALES</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>OFFSITE_CONVERSIONS</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="inlineStr">
+        <is>
+          <t>LOWEST_COST_WITHOUT_CAP</t>
+        </is>
+      </c>
+      <c r="E2" s="22" t="inlineStr">
+        <is>
+          <t>PURCHASE</t>
+        </is>
+      </c>
+      <c r="F2" s="22" t="inlineStr">
+        <is>
+          <t>LEARN_MORE</t>
+        </is>
+      </c>
+      <c r="G2" s="22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>home+recent</t>
+        </is>
+      </c>
+      <c r="I2" s="22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J2" s="22" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="K2" s="22" t="inlineStr">
+        <is>
+          <t>feed</t>
+        </is>
+      </c>
+      <c r="L2" s="22" t="inlineStr">
+        <is>
+          <t>stream</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>OUTCOME_LEADS</t>
+        </is>
+      </c>
+      <c r="B3" s="22" t="inlineStr">
+        <is>
+          <t>LANDING_PAGE_VIEWS</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t>LINK_CLICKS</t>
+        </is>
+      </c>
+      <c r="D3" s="22" t="inlineStr">
+        <is>
+          <t>LOWEST_COST_WITH_BID_CAP</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t>ADD_TO_CART</t>
+        </is>
+      </c>
+      <c r="F3" s="22" t="inlineStr">
+        <is>
+          <t>SHOP_NOW</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t>Men</t>
+        </is>
+      </c>
+      <c r="H3" s="22" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J3" s="22" t="inlineStr">
+        <is>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="L3" s="22" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>OUTCOME_TRAFFIC</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>LINK_CLICKS</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>POST_ENGAGEMENT</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>COST_CAP</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>INITIATE_CHECKOUT</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>SIGN_UP</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>recent</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
+        <is>
+          <t>desktop</t>
+        </is>
+      </c>
+      <c r="J4" s="22" t="inlineStr">
+        <is>
+          <t>audience_network</t>
+        </is>
+      </c>
+      <c r="K4" s="22" t="inlineStr">
+        <is>
+          <t>facebook_reels</t>
+        </is>
+      </c>
+      <c r="L4" s="22" t="inlineStr">
+        <is>
+          <t>reels</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>OUTCOME_AWARENESS</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>COMPLETE_REGISTRATION</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>SUBSCRIBE</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>travel_in</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>messenger</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>video_feeds</t>
+        </is>
+      </c>
+      <c r="L5" s="22" t="inlineStr">
+        <is>
+          <t>explore</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>OUTCOME_ENGAGEMENT</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>REACH</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>BOOK_TRAVEL</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>threads</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>marketplace</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>explore_home</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
           <t>OUTCOME_APP_PROMOTION</t>
         </is>
       </c>
@@ -1736,14 +3968,24 @@
           <t>LEAD_GENERATION</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>VIEW_CONTENT</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>CONTACT_US</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>search</t>
+        </is>
+      </c>
+      <c r="L7" s="22" t="inlineStr">
+        <is>
+          <t>profile_feed</t>
         </is>
       </c>
     </row>
@@ -1753,90 +3995,115 @@
           <t>THRUPLAY</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>SEARCH</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>DOWNLOAD</t>
         </is>
       </c>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>profile_feed</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>ig_search</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="D9" s="22" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>ADD_PAYMENT_INFO</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>GET_OFFER</t>
         </is>
       </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>right_hand_column</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>profile_reels</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="D10" s="22" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>SUBSCRIBE</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>GET_QUOTE</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="D11" s="22" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>START_TRIAL</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>APPLY_NOW</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="E12" s="22" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>BUY_NOW</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="E13" s="22" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>ORDER_NOW</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="E14" s="22" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>GET_STARTED</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="22" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>SEND_MESSAGE</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="E16" s="22" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>WATCH_MORE</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="E17" s="22" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>NO_BUTTON</t>
         </is>

--- a/spec/CAMPAIGN-TEMPLATE.xlsx
+++ b/spec/CAMPAIGN-TEMPLATE.xlsx
@@ -1296,7 +1296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1366,7 +1366,7 @@
           <t>bid_amount_minor</t>
         </is>
       </c>
-      <c r="H1" s="17" t="inlineStr">
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>countries</t>
         </is>
@@ -1563,7 +1563,7 @@
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>Q3 UK Retarget 30d</t>
+          <t>Q3 Spanish speakers WW</t>
         </is>
       </c>
       <c r="B3" s="19" t="inlineStr"/>
@@ -1580,26 +1580,14 @@
       </c>
       <c r="F3" s="19" t="inlineStr"/>
       <c r="G3" s="19" t="inlineStr"/>
-      <c r="H3" s="19" t="inlineStr">
-        <is>
-          <t>GB,IE</t>
-        </is>
-      </c>
+      <c r="H3" s="19" t="inlineStr"/>
       <c r="I3" s="19" t="inlineStr"/>
-      <c r="J3" s="19" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
+      <c r="J3" s="19" t="inlineStr"/>
       <c r="K3" s="19" t="inlineStr"/>
-      <c r="L3" s="19" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
+      <c r="L3" s="19" t="inlineStr"/>
       <c r="M3" s="19" t="inlineStr">
         <is>
-          <t>English (UK),English (US)</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="N3" s="19" t="inlineStr">
@@ -1615,16 +1603,8 @@
       </c>
       <c r="Q3" s="19" t="inlineStr"/>
       <c r="R3" s="19" t="inlineStr"/>
-      <c r="S3" s="19" t="inlineStr">
-        <is>
-          <t>Website visitors 30d</t>
-        </is>
-      </c>
-      <c r="T3" s="19" t="inlineStr">
-        <is>
-          <t>Purchasers 180d</t>
-        </is>
-      </c>
+      <c r="S3" s="19" t="inlineStr"/>
+      <c r="T3" s="19" t="inlineStr"/>
       <c r="U3" s="19" t="inlineStr">
         <is>
           <t>no</t>
@@ -1673,61 +1653,68 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>countries / excluded_countries: ISO codes, comma separated. See the Countries tab. e.g. GB,IE</t>
+          <t>countries: ISO codes comma separated (GB,IE), or 'worldwide'. See the Countries tab.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>cities / regions: names, comma separated. e.g. London,Manchester  (Claude resolves them to Meta IDs)</t>
+          <t xml:space="preserve">   Targeting a LANGUAGE only? Leave countries blank and fill languages -&gt; worldwide in that language.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>location_types: home+recent (default), home, recent, travel_in</t>
+          <t>cities / regions: names, comma separated. e.g. London,Manchester  (Claude resolves them to Meta IDs)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>languages: names EXACTLY as on the Languages tab, comma separated. Blank = all languages.</t>
+          <t>location_types: home+recent (default), home, recent, travel_in</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>genders: All / Men / Women.   advantage_audience: yes lets Meta expand beyond your targeting.</t>
+          <t>languages: names EXACTLY as on the Languages tab, comma separated. Blank = all languages.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>interests / custom_audiences: names, comma separated. Claude resolves and CONFIRMS each one before building.</t>
+          <t>genders: All / Men / Women.   advantage_audience: yes lets Meta expand beyond your targeting.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>publisher_platforms / positions: blank = Advantage+ placements (all). Fill only to restrict.</t>
+          <t>interests / custom_audiences: names, comma separated. Claude resolves and CONFIRMS each one before building.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>budgets: fill daily OR lifetime, never both. Leave BOTH blank if the campaign is CBO.</t>
+          <t>publisher_platforms / positions: blank = Advantage+ placements (all). Fill only to restrict.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>budgets: fill daily OR lifetime, never both. Leave BOTH blank if the campaign is CBO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>start_time / end_time: 2026-09-01T00:00:00+0300</t>
         </is>
@@ -1770,7 +1757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1867,12 +1854,12 @@
       </c>
       <c r="D2" s="21" t="inlineStr">
         <is>
-          <t>Three months of clear skin, or your money back. Over 12,000 five star reviews.</t>
+          <t>Three months of clear skin, or your money back. | Over 12,000 five star reviews. | Results by week six, or you pay nothing.</t>
         </is>
       </c>
       <c r="E2" s="21" t="inlineStr">
         <is>
-          <t>Clinically proven</t>
+          <t>Clinically proven | Dermatologist tested | 90-day guarantee</t>
         </is>
       </c>
       <c r="F2" s="21" t="inlineStr">
@@ -2012,6 +1999,27 @@
       <c r="A9" s="20" t="inlineStr">
         <is>
           <t>cta / link / url_tags / page_id / instagram_user_id: blank inherits the Campaign tab default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>SEVERAL PRIMARY TEXTS OR HEADLINES IN ONE AD: separate them with |   Hook one | Hook two | Hook three</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Meta rotates them within the single ad and learns which wins. Max 5 texts and 5 headlines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Row 2 above shows it. Commas are NOT separators - ad copy is full of commas.</t>
         </is>
       </c>
     </row>
